--- a/기능명세서_사용자용.xlsx
+++ b/기능명세서_사용자용.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1002,75 +1002,75 @@
       </c>
     </row>
     <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="6" t="n"/>
+      <c r="A21" s="7" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
+          <t>조건 설명 보기</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>어려운 조건 옆 ⓘ 버튼을 누르면 그 조건이 무슨 뜻인지 쉬운 말로 알려줍니다.</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>조건 옆 ⓘ 버튼</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
           <t>오늘의 인기 종목</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>거래량·거래대금이 많은 회사, 많이 오른 회사, 외국인·기관이 많이 산 회사 순위를 보여줍니다.</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>시장 현황 화면</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>편하게 보기</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>검색으로 찾기</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>회사 이름이나 번호를 입력해 바로 찾아볼 수 있습니다.</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>화면 위쪽 검색창</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>살짝 미리보기</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>목록에서 회사 위에 마우스를 올리면, 작은 그래프와 한 줄 요약을 옆에서 미리 보여줍니다.</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>오른쪽 미리보기 칸</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
         </is>
       </c>
     </row>
@@ -1078,43 +1078,66 @@
       <c r="A24" s="7" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
+          <t>살짝 미리보기</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>목록에서 회사 위에 마우스를 올리면, 작은 그래프와 한 줄 요약을 옆에서 미리 보여줍니다.</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>오른쪽 미리보기 칸</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
           <t>뒤로가기</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>회사를 보다가 뒤로가기를 누르면, 보던 목록의 그 자리로 그대로 돌아옵니다.</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>전체 화면</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="6" t="n"/>
-      <c r="B25" s="3" t="inlineStr">
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>큰 글씨 모드</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>버튼 하나로 글씨·그래프·여백까지 화면 전체를 1.3배 크게 키워, 작은 글씨가 불편한 분도 편하게 볼 수 있습니다.</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>오른쪽 아래 큰 글씨 전환 버튼</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -1124,11 +1147,11 @@
   <mergeCells count="7">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A23:A26"/>
     <mergeCell ref="A11:A14"/>
     <mergeCell ref="A15:A18"/>
     <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A19:A22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/기능명세서_사용자용.xlsx
+++ b/기능명세서_사용자용.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -833,7 +833,7 @@
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="6" t="n"/>
+      <c r="A14" s="7" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
           <t>매수·매도 가격 안내</t>
@@ -856,42 +856,42 @@
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>유사 패턴 찾기</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>지금 차트와 모양이 비슷했던 과거 사례를 다른 종목에서 찾아주고, 그때 이후에 얼마나 올랐는지/내렸는지를 알려줍니다.</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>유사 패턴 검색 카드</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>AI 전망 분석</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>종합 점수</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>가격 흐름, 뉴스, 회사 재무를 모두 따져 이 회사가 좋은 신호인지 나쁜 신호인지 점수로 알려줍니다.</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>전망 분석 화면</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="7" t="n"/>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>뉴스·공시 해석</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>AI가 최신 뉴스와 공시를 읽고, 호재인지 악재인지 쉬운 말로 요약해 줍니다.</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -909,95 +909,95 @@
       <c r="A17" s="7" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
+          <t>뉴스·공시 해석</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>AI가 최신 뉴스와 공시를 읽고, 호재인지 악재인지 쉬운 말로 요약해 줍니다.</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>전망 분석 화면</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
           <t>판단의 근거 보기</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>점수가 왜 이렇게 나왔는지, 어떤 뉴스·공시를 보고 판단했는지 원문까지 확인할 수 있습니다.</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>근거 목록 화면</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="6" t="n"/>
-      <c r="B18" s="3" t="inlineStr">
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>내 보유 종목 손익</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>산 가격과 수량을 넣으면 지금 얼마 벌었는지/잃었는지, 본전이 되려면 얼마나 올라야 하는지 계산해 줍니다.</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>보유 종목 카드</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>종목 찾기</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>조건으로 찾기</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>'거래량이 갑자기 늘어난 회사', '외국인이 계속 사는 회사' 같은 조건을 골라, 그에 맞는 회사들을 찾아 줍니다.</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>조건 검색 화면</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>2026-05-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="7" t="n"/>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>조건 세부 조정</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>각 조건의 기준(며칠 연속인지, 몇 배인지 등)을 직접 바꿀 수 있습니다.</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>조건 옆 설정 버튼</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -1005,95 +1005,95 @@
       <c r="A21" s="7" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
+          <t>조건 세부 조정</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>각 조건의 기준(며칠 연속인지, 몇 배인지 등)을 직접 바꿀 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>조건 옆 설정 버튼</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="7" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
           <t>조건 설명 보기</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>어려운 조건 옆 ⓘ 버튼을 누르면 그 조건이 무슨 뜻인지 쉬운 말로 알려줍니다.</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>조건 옆 ⓘ 버튼</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="6" t="n"/>
-      <c r="B22" s="3" t="inlineStr">
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>오늘의 인기 종목</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>거래량·거래대금이 많은 회사, 많이 오른 회사, 외국인·기관이 많이 산 회사 순위를 보여줍니다.</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>시장 현황 화면</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>편하게 보기</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>검색으로 찾기</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>회사 이름이나 번호를 입력해 바로 찾아볼 수 있습니다.</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>화면 위쪽 검색창</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="7" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>살짝 미리보기</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>목록에서 회사 위에 마우스를 올리면, 작은 그래프와 한 줄 요약을 옆에서 미리 보여줍니다.</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>오른쪽 미리보기 칸</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
         </is>
       </c>
     </row>
@@ -1101,43 +1101,66 @@
       <c r="A25" s="7" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
+          <t>살짝 미리보기</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>목록에서 회사 위에 마우스를 올리면, 작은 그래프와 한 줄 요약을 옆에서 미리 보여줍니다.</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>오른쪽 미리보기 칸</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
           <t>뒤로가기</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>회사를 보다가 뒤로가기를 누르면, 보던 목록의 그 자리로 그대로 돌아옵니다.</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>전체 화면</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="6" t="n"/>
-      <c r="B26" s="3" t="inlineStr">
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>큰 글씨 모드</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>버튼 하나로 글씨·그래프·여백까지 화면 전체를 1.3배 크게 키워, 작은 글씨가 불편한 분도 편하게 볼 수 있습니다.</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>오른쪽 아래 큰 글씨 전환 버튼</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -1147,11 +1170,11 @@
   <mergeCells count="7">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="A20:A23"/>
     <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A11:A15"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/기능명세서_사용자용.xlsx
+++ b/기능명세서_사용자용.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -856,7 +856,7 @@
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="6" t="n"/>
+      <c r="A15" s="7" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
           <t>유사 패턴 찾기</t>
@@ -864,7 +864,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>지금 차트와 모양이 비슷했던 과거 사례를 다른 종목에서 찾아주고, 그때 이후에 얼마나 올랐는지/내렸는지를 알려줍니다.</t>
+          <t>지금 차트와 모양이 비슷했던 과거 사례를 다른 종목에서 찾아주고, 그때 이후에 얼마나 올랐는지/내렸는지를 알려줍니다. 비교 기준(DTW/피어슨/스피어만), 찾을 개수, 최소 유사도를 직접 정할 수 있습니다.</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -879,42 +879,42 @@
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>유사 사례 차트 비교</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>찾은 사례를 누르면 지금 종목과 그 사례의 실제 차트를 나란히 보여줍니다. 세로선(현재 시점) 왼쪽이 비슷했던 구간, 오른쪽이 그 뒤 실제로 흘러간 흐름입니다.</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>유사 패턴 비교 차트</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>AI 전망 분석</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>종합 점수</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>가격 흐름, 뉴스, 회사 재무를 모두 따져 이 회사가 좋은 신호인지 나쁜 신호인지 점수로 알려줍니다.</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>전망 분석 화면</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="7" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>뉴스·공시 해석</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>AI가 최신 뉴스와 공시를 읽고, 호재인지 악재인지 쉬운 말로 요약해 줍니다.</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -932,95 +932,95 @@
       <c r="A18" s="7" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>뉴스·공시 해석</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>AI가 최신 뉴스와 공시를 읽고, 호재인지 악재인지 쉬운 말로 요약해 줍니다.</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>전망 분석 화면</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
           <t>판단의 근거 보기</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>점수가 왜 이렇게 나왔는지, 어떤 뉴스·공시를 보고 판단했는지 원문까지 확인할 수 있습니다.</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>근거 목록 화면</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>내 보유 종목 손익</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>산 가격과 수량을 넣으면 지금 얼마 벌었는지/잃었는지, 본전이 되려면 얼마나 올라야 하는지 계산해 줍니다.</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>보유 종목 카드</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>종목 찾기</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>조건으로 찾기</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>'거래량이 갑자기 늘어난 회사', '외국인이 계속 사는 회사' 같은 조건을 골라, 그에 맞는 회사들을 찾아 줍니다.</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>조건 검색 화면</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>2026-05-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="7" t="n"/>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>조건 세부 조정</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>각 조건의 기준(며칠 연속인지, 몇 배인지 등)을 직접 바꿀 수 있습니다.</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>조건 옆 설정 버튼</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -1028,95 +1028,95 @@
       <c r="A22" s="7" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
+          <t>조건 세부 조정</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>각 조건의 기준(며칠 연속인지, 몇 배인지 등)을 직접 바꿀 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>조건 옆 설정 버튼</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
           <t>조건 설명 보기</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>어려운 조건 옆 ⓘ 버튼을 누르면 그 조건이 무슨 뜻인지 쉬운 말로 알려줍니다.</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>조건 옆 ⓘ 버튼</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="6" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>오늘의 인기 종목</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>거래량·거래대금이 많은 회사, 많이 오른 회사, 외국인·기관이 많이 산 회사 순위를 보여줍니다.</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>시장 현황 화면</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>편하게 보기</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>검색으로 찾기</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>회사 이름이나 번호를 입력해 바로 찾아볼 수 있습니다.</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>화면 위쪽 검색창</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="7" t="n"/>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>살짝 미리보기</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>목록에서 회사 위에 마우스를 올리면, 작은 그래프와 한 줄 요약을 옆에서 미리 보여줍니다.</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>오른쪽 미리보기 칸</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
         </is>
       </c>
     </row>
@@ -1124,43 +1124,66 @@
       <c r="A26" s="7" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
+          <t>살짝 미리보기</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>목록에서 회사 위에 마우스를 올리면, 작은 그래프와 한 줄 요약을 옆에서 미리 보여줍니다.</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>오른쪽 미리보기 칸</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
           <t>뒤로가기</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>회사를 보다가 뒤로가기를 누르면, 보던 목록의 그 자리로 그대로 돌아옵니다.</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>전체 화면</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="42" customHeight="1">
-      <c r="A27" s="6" t="n"/>
-      <c r="B27" s="3" t="inlineStr">
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>큰 글씨 모드</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>버튼 하나로 글씨·그래프·여백까지 화면 전체를 1.3배 크게 키워, 작은 글씨가 불편한 분도 편하게 볼 수 있습니다.</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>오른쪽 아래 큰 글씨 전환 버튼</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -1170,11 +1193,11 @@
   <mergeCells count="7">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="A21:A24"/>
     <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A11:A15"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A25:A28"/>
+    <mergeCell ref="A11:A16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/기능명세서_사용자용.xlsx
+++ b/기능명세서_사용자용.xlsx
@@ -38,7 +38,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +48,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00548235"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -115,12 +120,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -132,10 +137,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -857,22 +871,22 @@
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="7" t="n"/>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>유사 패턴 찾기</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>지금 차트와 모양이 비슷했던 과거 사례를 다른 종목에서 찾아주고, 그때 이후에 얼마나 올랐는지/내렸는지를 알려줍니다. 비교 기준(DTW/피어슨/스피어만), 찾을 개수, 최소 유사도를 직접 정할 수 있습니다.</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>유사 패턴 검색 카드</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
@@ -880,22 +894,22 @@
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="6" t="n"/>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>유사 사례 차트 비교</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>찾은 사례를 누르면 지금 종목과 그 사례의 실제 차트를 나란히 보여줍니다. 세로선(현재 시점) 왼쪽이 비슷했던 구간, 오른쪽이 그 뒤 실제로 흘러간 흐름입니다.</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>유사 패턴 비교 차트</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>

--- a/기능명세서_사용자용.xlsx
+++ b/기능명세서_사용자용.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -871,22 +871,22 @@
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="7" t="n"/>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>유사 패턴 찾기</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>지금 차트와 모양이 비슷했던 과거 사례를 다른 종목에서 찾아주고, 그때 이후에 얼마나 올랐는지/내렸는지를 알려줍니다. 비교 기준(DTW/피어슨/스피어만), 찾을 개수, 최소 유사도를 직접 정할 수 있습니다.</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>유사 패턴 검색 카드</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
@@ -894,22 +894,22 @@
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="6" t="n"/>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>유사 사례 차트 비교</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>찾은 사례를 누르면 지금 종목과 그 사례의 실제 차트를 나란히 보여줍니다. 세로선(현재 시점) 왼쪽이 비슷했던 구간, 오른쪽이 그 뒤 실제로 흘러간 흐름입니다.</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>유사 패턴 비교 차트</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -1017,24 +1017,24 @@
           <t>종목 찾기</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>조건으로 찾기</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>'거래량이 갑자기 늘어난 회사', '외국인이 계속 사는 회사' 같은 조건을 골라, 그에 맞는 회사들을 찾아 줍니다.</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>조건 검색 화면</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>업종별 추천</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>반도체, 제약, 화학 등 29개 업종 중 하나를 누르면 그 업종에서 최근 가격과 거래량이 가장 좋은 종목 3개를 골라줍니다.</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>업종 추천 화면</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>
@@ -1042,22 +1042,22 @@
       <c r="A22" s="7" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>조건 세부 조정</t>
+          <t>조건으로 찾기</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>각 조건의 기준(며칠 연속인지, 몇 배인지 등)을 직접 바꿀 수 있습니다.</t>
+          <t>'거래량이 갑자기 늘어난 회사', '외국인이 계속 사는 회사' 같은 조건을 골라, 그에 맞는 회사들을 찾아 줍니다.</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>조건 옆 설정 버튼</t>
+          <t>조건 검색 화면</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -1065,95 +1065,95 @@
       <c r="A23" s="7" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
+          <t>조건 세부 조정</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>각 조건의 기준(며칠 연속인지, 몇 배인지 등)을 직접 바꿀 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>조건 옆 설정 버튼</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
           <t>조건 설명 보기</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>어려운 조건 옆 ⓘ 버튼을 누르면 그 조건이 무슨 뜻인지 쉬운 말로 알려줍니다.</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>조건 옆 ⓘ 버튼</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="6" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>오늘의 인기 종목</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>거래량·거래대금이 많은 회사, 많이 오른 회사, 외국인·기관이 많이 산 회사 순위를 보여줍니다.</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>시장 현황 화면</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>편하게 보기</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>검색으로 찾기</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>회사 이름이나 번호를 입력해 바로 찾아볼 수 있습니다.</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>화면 위쪽 검색창</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>2026-05-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="7" t="n"/>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>살짝 미리보기</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>목록에서 회사 위에 마우스를 올리면, 작은 그래프와 한 줄 요약을 옆에서 미리 보여줍니다.</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>오른쪽 미리보기 칸</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
         </is>
       </c>
     </row>
@@ -1161,43 +1161,66 @@
       <c r="A27" s="7" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
+          <t>살짝 미리보기</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>목록에서 회사 위에 마우스를 올리면, 작은 그래프와 한 줄 요약을 옆에서 미리 보여줍니다.</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>오른쪽 미리보기 칸</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
           <t>뒤로가기</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>회사를 보다가 뒤로가기를 누르면, 보던 목록의 그 자리로 그대로 돌아옵니다.</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>전체 화면</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="42" customHeight="1">
-      <c r="A28" s="6" t="n"/>
-      <c r="B28" s="3" t="inlineStr">
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>큰 글씨 모드</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>버튼 하나로 글씨·그래프·여백까지 화면 전체를 1.3배 크게 키워, 작은 글씨가 불편한 분도 편하게 볼 수 있습니다.</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>오른쪽 아래 큰 글씨 전환 버튼</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -1207,10 +1230,10 @@
   <mergeCells count="7">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A21:A25"/>
+    <mergeCell ref="A26:A29"/>
     <mergeCell ref="A17:A20"/>
-    <mergeCell ref="A21:A24"/>
     <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A25:A28"/>
     <mergeCell ref="A11:A16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
